--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -1723,7 +1723,7 @@
         <v>121654531</v>
       </c>
       <c r="B12" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -1723,7 +1723,7 @@
         <v>121654531</v>
       </c>
       <c r="B12" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
